--- a/data/trans_bre/P1413-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P1413-Clase-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8,58</t>
+          <t>8,62</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>58,63%</t>
+          <t>57,92%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-6,38; 4,6</t>
+          <t>-5,84; 4,22</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,16; 10,38</t>
+          <t>0,72; 10,25</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,22; 4,03</t>
+          <t>-4,35; 3,69</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,1; 13,01</t>
+          <t>4,29; 13,16</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-38,87; 37,57</t>
+          <t>-36,95; 38,03</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,36; 174,49</t>
+          <t>5,8; 177,22</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-44,8; 61,94</t>
+          <t>-42,91; 56,98</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>24,05; 106,01</t>
+          <t>25,97; 102,21</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>10,19</t>
+          <t>11,34</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>59,97%</t>
+          <t>68,06%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,11; 12,1</t>
+          <t>2,42; 12,18</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,96; 10,8</t>
+          <t>1,12; 10,55</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,2; 10,75</t>
+          <t>1,84; 10,44</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5,05; 15,34</t>
+          <t>6,64; 16,56</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>14,11; 153,48</t>
+          <t>18,38; 157,41</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,28; 170,02</t>
+          <t>9,85; 164,66</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>28,87; 300,27</t>
+          <t>19,05; 288,55</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>25,62; 108,73</t>
+          <t>34,39; 118,02</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>22,82</t>
+          <t>14,33</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>163,71%</t>
+          <t>65,53%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,02; 10,41</t>
+          <t>-4,34; 10,1</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,17; 10,6</t>
+          <t>0,05; 10,78</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,5; 19,98</t>
+          <t>6,31; 20,61</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>12,55; 35,67</t>
+          <t>7,5; 21,2</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-20,95; 61,27</t>
+          <t>-21,08; 63,87</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 118,65</t>
+          <t>-2,59; 117,86</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>69,03; 298,93</t>
+          <t>70,05; 314,73</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>54,83; 606,21</t>
+          <t>29,72; 108,65</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>20,61</t>
+          <t>6,2</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
+          <t>29,47%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-4,88; 2,56</t>
+          <t>-4,65; 2,42</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,82; 8,7</t>
+          <t>1,94; 8,48</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,88; 6,82</t>
+          <t>0,93; 6,9</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,77; 43,6</t>
+          <t>2,59; 9,81</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-23,17; 12,87</t>
+          <t>-21,37; 12,98</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>14,2; 86,03</t>
+          <t>15,33; 86,89</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,32; 85,6</t>
+          <t>8,94; 85,75</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>16,38; 223,64</t>
+          <t>11,56; 50,84</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>14,06</t>
+          <t>18,83</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>63,97%</t>
+          <t>90,13%</t>
         </is>
       </c>
     </row>
@@ -1060,49 +1060,49 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,21; 7,58</t>
+          <t>-3,02; 7,53</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>10,75; 18,8</t>
+          <t>10,36; 18,4</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,54; 9,02</t>
+          <t>1,33; 9,28</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,65; 20,65</t>
+          <t>14,28; 23,26</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-14,5; 46,67</t>
+          <t>-13,91; 46,58</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>101,68; 289,01</t>
+          <t>99,52; 281,25</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,09; 93,08</t>
+          <t>7,87; 89,08</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>20,98; 106,47</t>
+          <t>60,29; 132,46</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>21,47</t>
+          <t>21,39</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>244,74%</t>
+          <t>246,4%</t>
         </is>
       </c>
     </row>
@@ -1160,32 +1160,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>15,87; 20,97</t>
+          <t>15,5; 20,94</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>13,63; 20,16</t>
+          <t>13,78; 20,4</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>11,12; 15,67</t>
+          <t>11,27; 15,99</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>13,29; 26,51</t>
+          <t>13,8; 26,53</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>440,73; 2793,88</t>
+          <t>401,79; 2272,44</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>269,8; 2427,32</t>
+          <t>256,31; 2478,67</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>80,25; 586,35</t>
+          <t>83,26; 565,28</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16,42</t>
+          <t>12,12</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>93,6%</t>
+          <t>64,94%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,25; 4,83</t>
+          <t>1,37; 5,05</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>7,47; 10,81</t>
+          <t>7,42; 10,85</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4,04; 7,17</t>
+          <t>4,07; 7,24</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>11,26; 30,31</t>
+          <t>10,22; 13,84</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>7,23; 31,99</t>
+          <t>8,07; 32,62</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>75,57; 129,66</t>
+          <t>75,33; 130,9</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>45,18; 96,74</t>
+          <t>44,2; 95,84</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>59,1; 176,56</t>
+          <t>51,86; 77,98</t>
         </is>
       </c>
     </row>
